--- a/Wi-Fi/Wi-Fi_Sizing_Script_9.0.xlsx
+++ b/Wi-Fi/Wi-Fi_Sizing_Script_9.0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sainamithanagireddy/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD587F2-3DA0-D94B-B82D-E7CE45BF7A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D6EB21-472B-7442-B265-3E42AAAC9225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29920" windowHeight="16960" firstSheet="1" activeTab="2" xr2:uid="{CD935837-EFB7-7640-805F-6441372B141E}"/>
   </bookViews>
@@ -873,10 +873,10 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1202,7 +1202,7 @@
     <row r="1" spans="3:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="3:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="3:5" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="38" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="10" t="s">
@@ -1213,7 +1213,7 @@
       </c>
     </row>
     <row r="4" spans="3:5" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="37"/>
+      <c r="C4" s="38"/>
       <c r="D4" s="9" t="s">
         <v>2</v>
       </c>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="C6" s="23">
         <f xml:space="preserve"> (C62 * F10) + (C71 * F11) + (C75 * F14)</f>
-        <v>10673</v>
+        <v>3196</v>
       </c>
       <c r="D6" s="33" t="s">
         <v>166</v>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="C7" s="24">
         <f xml:space="preserve"> (C62 * F10)/F18 + (C71 * F11)/F18 + (C75 * F14)/F18</f>
-        <v>35.576666666666668</v>
+        <v>10.653333333333334</v>
       </c>
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
@@ -2848,7 +2848,7 @@
         <v>4</v>
       </c>
       <c r="D50" s="20"/>
-      <c r="E50" s="38" t="s">
+      <c r="E50" s="37" t="s">
         <v>167</v>
       </c>
       <c r="F50" s="27">
@@ -2994,8 +2994,8 @@
         <v>159</v>
       </c>
       <c r="C62" s="21">
-        <f>SUMPRODUCT(C10:C31, F18:F39)+SUM(C32:C60)</f>
-        <v>10364</v>
+        <f>SUMPRODUCT(C10:C31, F21:F42)+SUM(C32:C60)</f>
+        <v>2887</v>
       </c>
       <c r="D62" s="20"/>
       <c r="E62" s="20"/>
